--- a/data/raw/Component_Category_COMC_554__WindowsNew.xlsx
+++ b/data/raw/Component_Category_COMC_554__WindowsNew.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S7NM\Desktop\EOSL\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DC07315-E03E-4557-9B83-FDD4FDD54D7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8890BE9D-0E5A-4EC8-83B3-3350ED8A80A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="825" activeTab="2" xr2:uid="{256E2C74-0424-4548-BE1E-F47234AD9C9F}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="825" activeTab="3" xr2:uid="{256E2C74-0424-4548-BE1E-F47234AD9C9F}"/>
   </bookViews>
   <sheets>
     <sheet name="Windows" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3623" uniqueCount="1604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3715" uniqueCount="1625">
   <si>
     <t>Nr.</t>
   </si>
@@ -4864,6 +4864,69 @@
   </si>
   <si>
     <t>Windows Server 2003</t>
+  </si>
+  <si>
+    <t>Microsoft Message Queuing (MSMQ)</t>
+  </si>
+  <si>
+    <t>6.3.9600</t>
+  </si>
+  <si>
+    <t>10.0.14393</t>
+  </si>
+  <si>
+    <t>10.0.20348</t>
+  </si>
+  <si>
+    <t>Microsoft SQL Server Integration Services (SSIS)</t>
+  </si>
+  <si>
+    <t>11.0.7512.11</t>
+  </si>
+  <si>
+    <t>12.0.6433.1</t>
+  </si>
+  <si>
+    <t>12.0.6449.1</t>
+  </si>
+  <si>
+    <t>13.0.6465.1</t>
+  </si>
+  <si>
+    <t>13.0.7060.1</t>
+  </si>
+  <si>
+    <t>13.0.7070.1</t>
+  </si>
+  <si>
+    <t>15.0.4440.1</t>
+  </si>
+  <si>
+    <t>EMC Avamar Client</t>
+  </si>
+  <si>
+    <t>19.8.100</t>
+  </si>
+  <si>
+    <t>19.8.100.83</t>
+  </si>
+  <si>
+    <t>19.10.100</t>
+  </si>
+  <si>
+    <t>Apache Tomcat</t>
+  </si>
+  <si>
+    <t>2021.6.7</t>
+  </si>
+  <si>
+    <t>2021.6.11</t>
+  </si>
+  <si>
+    <t>WildFly</t>
+  </si>
+  <si>
+    <t>8.2.1</t>
   </si>
 </sst>
 </file>
@@ -5486,21 +5549,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A83CC03C-72C0-4469-A020-B10F65145916}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" customWidth="1"/>
-    <col min="4" max="5" width="41.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="7" max="7" width="41.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="9" width="11.42578125" style="19" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" customWidth="1"/>
+    <col min="4" max="5" width="41.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" customWidth="1"/>
+    <col min="7" max="7" width="41.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="19" customWidth="1"/>
     <col min="10" max="10" width="19" style="19" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="11" max="259" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5532,7 +5595,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>4</v>
       </c>
@@ -5562,7 +5625,7 @@
         <v>47127</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>17</v>
       </c>
@@ -5592,7 +5655,7 @@
         <v>47400</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>21</v>
       </c>
@@ -5622,7 +5685,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>22</v>
       </c>
@@ -5652,7 +5715,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>23</v>
       </c>
@@ -5682,7 +5745,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>24</v>
       </c>
@@ -5712,7 +5775,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>25</v>
       </c>
@@ -5742,7 +5805,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>26</v>
       </c>
@@ -5772,7 +5835,7 @@
         <v>46399</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>27</v>
       </c>
@@ -5802,7 +5865,7 @@
         <v>46399</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>28</v>
       </c>
@@ -5832,7 +5895,7 @@
         <v>46399</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>29</v>
       </c>
@@ -5862,7 +5925,7 @@
         <v>47127</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>30</v>
       </c>
@@ -5892,7 +5955,7 @@
         <v>47127</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>31</v>
       </c>
@@ -5922,7 +5985,7 @@
         <v>47127</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>32</v>
       </c>
@@ -5952,7 +6015,7 @@
         <v>48135</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>33</v>
       </c>
@@ -5982,7 +6045,7 @@
         <v>48135</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>34</v>
       </c>
@@ -6012,7 +6075,7 @@
         <v>48135</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>35</v>
       </c>
@@ -6042,7 +6105,7 @@
         <v>49262</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>36</v>
       </c>
@@ -6072,7 +6135,7 @@
         <v>49262</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>37</v>
       </c>
@@ -6096,7 +6159,7 @@
         <v>42199</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>38</v>
       </c>
@@ -6120,7 +6183,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>39</v>
       </c>
@@ -6144,7 +6207,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D23" s="5" t="s">
         <v>1603</v>
       </c>
@@ -6173,17 +6236,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F7F3066-14AF-4358-84ED-194BE9C5CA05}">
   <dimension ref="A1:J23"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="5" width="12.7109375" customWidth="1"/>
-    <col min="6" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="11.42578125" style="19" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="10" width="11.44140625" style="19" customWidth="1"/>
+    <col min="11" max="259" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6215,7 +6278,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -6245,7 +6308,7 @@
         <v>42855</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -6275,7 +6338,7 @@
         <v>43830</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6305,7 +6368,7 @@
         <v>45046</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -6335,7 +6398,7 @@
         <v>43465</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -6365,7 +6428,7 @@
         <v>44469</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -6395,7 +6458,7 @@
         <v>44895</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -6425,7 +6488,7 @@
         <v>45962</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -6455,7 +6518,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -6485,7 +6548,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -6515,7 +6578,7 @@
         <v>46356</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -6545,7 +6608,7 @@
         <v>46752</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -6575,7 +6638,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -6605,7 +6668,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -6635,7 +6698,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -6665,7 +6728,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -6695,7 +6758,7 @@
         <v>45657</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -6725,7 +6788,7 @@
         <v>46388</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -6748,7 +6811,7 @@
         <v>44104</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -6773,7 +6836,7 @@
         <v>44104</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -6798,7 +6861,7 @@
         <v>44104</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -6823,7 +6886,7 @@
         <v>44104</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -6859,19 +6922,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{788C2E7A-BD2F-4C2A-9978-85454F3B2F95}">
   <dimension ref="A1:J63"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="5" width="30.28515625" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="7" width="30.28515625" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="11.42578125" style="19" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="5" width="30.33203125" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="7" width="30.33203125" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="10" width="11.44140625" style="19" customWidth="1"/>
+    <col min="11" max="259" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6903,7 +6966,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -6933,7 +6996,7 @@
         <v>42825</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -6963,7 +7026,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -6993,7 +7056,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -7023,7 +7086,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -7053,7 +7116,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -7083,7 +7146,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -7113,7 +7176,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -7143,7 +7206,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -7173,7 +7236,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -7203,7 +7266,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -7233,7 +7296,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -7263,7 +7326,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -7293,7 +7356,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -7323,7 +7386,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -7353,7 +7416,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -7383,7 +7446,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -7413,7 +7476,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -7443,7 +7506,7 @@
         <v>46905</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -7473,7 +7536,7 @@
         <v>40543</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -7503,7 +7566,7 @@
         <v>43647</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -7533,7 +7596,7 @@
         <v>44926</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -7563,7 +7626,7 @@
         <v>46844</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -7593,7 +7656,7 @@
         <v>48305</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -7623,7 +7686,7 @@
         <v>49035</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -7649,7 +7712,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -7675,7 +7738,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -7701,7 +7764,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -7727,7 +7790,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -7753,7 +7816,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -7781,7 +7844,7 @@
         <v>42825</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -7809,7 +7872,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -7837,7 +7900,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -7865,7 +7928,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -7893,7 +7956,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -7921,7 +7984,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -7949,7 +8012,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -7977,7 +8040,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -8005,7 +8068,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -8033,7 +8096,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -8061,7 +8124,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -8089,7 +8152,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -8117,7 +8180,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -8145,7 +8208,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -8173,7 +8236,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -8201,7 +8264,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -8227,7 +8290,7 @@
         <v>42825</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -8253,7 +8316,7 @@
         <v>42825</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -8279,7 +8342,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -8305,7 +8368,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -8331,7 +8394,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -8357,7 +8420,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -8383,7 +8446,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -8411,7 +8474,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -8439,7 +8502,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -8462,7 +8525,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -8485,7 +8548,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -8508,7 +8571,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -8531,7 +8594,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -8554,7 +8617,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -8577,7 +8640,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -8600,7 +8663,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="H63" s="5"/>
     </row>
   </sheetData>
@@ -8613,19 +8676,13 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{330FE0E5-D58A-4703-9124-93717C598703}">
-  <dimension ref="A1:J25"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J41"/>
+  <sheetFormatPr defaultColWidth="20.21875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
-    <col min="4" max="5" width="22.7109375" customWidth="1"/>
-    <col min="6" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="11.42578125" style="19" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="9" max="10" width="20.21875" style="19"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -8657,7 +8714,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -8687,7 +8744,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -8717,7 +8774,7 @@
         <v>47848</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8747,7 +8804,7 @@
         <v>42929</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -8777,7 +8834,7 @@
         <v>44531</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -8807,7 +8864,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
@@ -8837,7 +8894,7 @@
         <v>42064</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
@@ -8867,7 +8924,7 @@
         <v>41608</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
@@ -8897,7 +8954,7 @@
         <v>41517</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -8927,7 +8984,7 @@
         <v>44561</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
@@ -8957,7 +9014,7 @@
         <v>42216</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
@@ -8987,7 +9044,7 @@
         <v>42551</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>12</v>
       </c>
@@ -9017,7 +9074,7 @@
         <v>44592</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -9047,7 +9104,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -9077,7 +9134,7 @@
         <v>45078</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -9107,7 +9164,7 @@
         <v>46357</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>16</v>
       </c>
@@ -9137,7 +9194,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>17</v>
       </c>
@@ -9167,7 +9224,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>18</v>
       </c>
@@ -9197,7 +9254,7 @@
         <v>38777</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>19</v>
       </c>
@@ -9227,7 +9284,7 @@
         <v>39753</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>20</v>
       </c>
@@ -9257,7 +9314,7 @@
         <v>40816</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>21</v>
       </c>
@@ -9287,41 +9344,537 @@
         <v>41608</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A23" s="2"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A25" s="2"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21" t="s">
+        <v>1605</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I23" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J23" s="22">
+        <v>43844</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="23"/>
+      <c r="C24" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D24" s="23" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E24" s="23"/>
+      <c r="F24" s="23" t="s">
+        <v>1606</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I24" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J24" s="24">
+        <v>46398</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21" t="s">
+        <v>1607</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>1604</v>
+      </c>
+      <c r="H25" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I25" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J25" s="22">
+        <v>11331</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="23"/>
+      <c r="C26" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E26" s="23"/>
+      <c r="F26" s="23" t="s">
+        <v>1609</v>
+      </c>
+      <c r="G26" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J26" s="24">
+        <v>44754</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H27" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J27" s="22">
+        <v>45482</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="23"/>
+      <c r="C28" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E28" s="23"/>
+      <c r="F28" s="23" t="s">
+        <v>1611</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I28" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J28" s="24">
+        <v>45482</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D29" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H29" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I29" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J29" s="22">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="23"/>
+      <c r="C30" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E30" s="23"/>
+      <c r="F30" s="23" t="s">
+        <v>1613</v>
+      </c>
+      <c r="G30" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I30" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J30" s="24">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D31" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21" t="s">
+        <v>1614</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H31" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I31" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J31" s="22">
+        <v>46217</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="23"/>
+      <c r="C32" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E32" s="23"/>
+      <c r="F32" s="23" t="s">
+        <v>1615</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>1608</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I32" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J32" s="24">
+        <v>47491</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H33" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I33" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J33" s="22">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="23"/>
+      <c r="C34" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E34" s="23"/>
+      <c r="F34" s="23" t="s">
+        <v>1618</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I34" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J34" s="24">
+        <v>46234</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="21"/>
+      <c r="C35" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D35" s="21" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E35" s="21"/>
+      <c r="F35" s="21" t="s">
+        <v>1619</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>1616</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I35" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J35" s="22">
+        <v>47149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E36" s="23"/>
+      <c r="F36" s="23">
+        <v>8</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I36" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J36" s="24">
+        <v>43281</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="21"/>
+      <c r="C37" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D37" s="21" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E37" s="21"/>
+      <c r="F37" s="21">
+        <v>8.5</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H37" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I37" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J37" s="22">
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="23"/>
+      <c r="C38" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E38" s="23"/>
+      <c r="F38" s="23">
+        <v>9</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I38" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J38" s="24">
+        <v>46657</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="21"/>
+      <c r="C39" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D39" s="21" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E39" s="21"/>
+      <c r="F39" s="21" t="s">
+        <v>1621</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H39" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I39" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J39" s="22">
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="E40" s="23"/>
+      <c r="F40" s="23" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G40" s="23" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="I40" s="24">
+        <v>28125</v>
+      </c>
+      <c r="J40" s="24">
+        <v>45382</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="21"/>
+      <c r="C41" s="21" t="s">
+        <v>1194</v>
+      </c>
+      <c r="D41" s="21" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E41" s="21"/>
+      <c r="F41" s="21" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>1623</v>
+      </c>
+      <c r="H41" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="I41" s="22">
+        <v>28125</v>
+      </c>
+      <c r="J41" s="22">
+        <v>42735</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0" footer="0"/>
@@ -9332,21 +9885,21 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17D1E04B-84B2-4035-8E1F-D4BF7B4CB1CB}">
   <dimension ref="A1:J132"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="10.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="6" max="6" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="10" width="10.109375" style="19" bestFit="1" customWidth="1"/>
+    <col min="11" max="259" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -9378,7 +9931,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -9408,7 +9961,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -9438,7 +9991,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -9468,7 +10021,7 @@
         <v>43307</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -9498,7 +10051,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -9528,7 +10081,7 @@
         <v>45968</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -9558,7 +10111,7 @@
         <v>45110</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -9588,7 +10141,7 @@
         <v>46065</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -9618,7 +10171,7 @@
         <v>46022</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -9648,7 +10201,7 @@
         <v>46722</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>13</v>
       </c>
@@ -9678,7 +10231,7 @@
         <v>40212</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>14</v>
       </c>
@@ -9708,7 +10261,7 @@
         <v>41464</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>18</v>
       </c>
@@ -9738,7 +10291,7 @@
         <v>43667</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>19</v>
       </c>
@@ -9768,7 +10321,7 @@
         <v>45222</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>20</v>
       </c>
@@ -9798,7 +10351,7 @@
         <v>45383</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>21</v>
       </c>
@@ -9828,7 +10381,7 @@
         <v>46302</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>22</v>
       </c>
@@ -9858,7 +10411,7 @@
         <v>46546</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>23</v>
       </c>
@@ -9888,7 +10441,7 @@
         <v>46849</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>24</v>
       </c>
@@ -9918,7 +10471,7 @@
         <v>47316</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>25</v>
       </c>
@@ -9948,7 +10501,7 @@
         <v>47506</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26</v>
       </c>
@@ -9978,7 +10531,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>27</v>
       </c>
@@ -10008,7 +10561,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>29</v>
       </c>
@@ -10038,7 +10591,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>32</v>
       </c>
@@ -10068,7 +10621,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>38</v>
       </c>
@@ -10098,7 +10651,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>39</v>
       </c>
@@ -10128,7 +10681,7 @@
         <v>44874</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>41</v>
       </c>
@@ -10158,7 +10711,7 @@
         <v>41737</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>42</v>
       </c>
@@ -10188,7 +10741,7 @@
         <v>42199</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>43</v>
       </c>
@@ -10218,7 +10771,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>44</v>
       </c>
@@ -10248,7 +10801,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>45</v>
       </c>
@@ -10278,7 +10831,7 @@
         <v>45209</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>49</v>
       </c>
@@ -10308,7 +10861,7 @@
         <v>42247</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>54</v>
       </c>
@@ -10338,7 +10891,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>55</v>
       </c>
@@ -10368,7 +10921,7 @@
         <v>43207</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>57</v>
       </c>
@@ -10398,7 +10951,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>58</v>
       </c>
@@ -10428,7 +10981,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>59</v>
       </c>
@@ -10458,7 +11011,7 @@
         <v>43942</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>60</v>
       </c>
@@ -10488,7 +11041,7 @@
         <v>44306</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>63</v>
       </c>
@@ -10518,7 +11071,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>64</v>
       </c>
@@ -10548,7 +11101,7 @@
         <v>44733</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>66</v>
       </c>
@@ -10578,7 +11131,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>67</v>
       </c>
@@ -10608,7 +11161,7 @@
         <v>45405</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>68</v>
       </c>
@@ -10638,7 +11191,7 @@
         <v>47267</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>69</v>
       </c>
@@ -10668,7 +11221,7 @@
         <v>47596</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>70</v>
       </c>
@@ -10698,7 +11251,7 @@
         <v>43007</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>71</v>
       </c>
@@ -10728,7 +11281,7 @@
         <v>44865</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>74</v>
       </c>
@@ -10758,7 +11311,7 @@
         <v>47573</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>79</v>
       </c>
@@ -10788,7 +11341,7 @@
         <v>39378</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>80</v>
       </c>
@@ -10818,7 +11371,7 @@
         <v>42735</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>81</v>
       </c>
@@ -10848,7 +11401,7 @@
         <v>44286</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>85</v>
       </c>
@@ -10878,7 +11431,7 @@
         <v>43281</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>86</v>
       </c>
@@ -10908,7 +11461,7 @@
         <v>45382</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>103</v>
       </c>
@@ -10938,7 +11491,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>103</v>
       </c>
@@ -10966,7 +11519,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>132</v>
       </c>
@@ -10996,7 +11549,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="5"/>
       <c r="C56" s="3"/>
@@ -11008,7 +11561,7 @@
       <c r="I56" s="6"/>
       <c r="J56" s="6"/>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -11020,7 +11573,7 @@
       <c r="I57" s="4"/>
       <c r="J57" s="4"/>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="5"/>
       <c r="C58" s="3"/>
@@ -11032,7 +11585,7 @@
       <c r="I58" s="6"/>
       <c r="J58" s="6"/>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -11044,7 +11597,7 @@
       <c r="I59" s="4"/>
       <c r="J59" s="4"/>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="5"/>
       <c r="C60" s="3"/>
@@ -11056,7 +11609,7 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -11068,7 +11621,7 @@
       <c r="I61" s="4"/>
       <c r="J61" s="4"/>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="5"/>
       <c r="C62" s="3"/>
@@ -11080,7 +11633,7 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6"/>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -11092,7 +11645,7 @@
       <c r="I63" s="4"/>
       <c r="J63" s="4"/>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="5"/>
       <c r="C64" s="3"/>
@@ -11104,7 +11657,7 @@
       <c r="I64" s="6"/>
       <c r="J64" s="6"/>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -11116,7 +11669,7 @@
       <c r="I65" s="4"/>
       <c r="J65" s="4"/>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="5"/>
       <c r="C66" s="3"/>
@@ -11128,7 +11681,7 @@
       <c r="I66" s="6"/>
       <c r="J66" s="6"/>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -11140,7 +11693,7 @@
       <c r="I67" s="4"/>
       <c r="J67" s="4"/>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="5"/>
       <c r="C68" s="3"/>
@@ -11152,7 +11705,7 @@
       <c r="I68" s="6"/>
       <c r="J68" s="6"/>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -11164,7 +11717,7 @@
       <c r="I69" s="4"/>
       <c r="J69" s="4"/>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="5"/>
       <c r="C70" s="3"/>
@@ -11176,7 +11729,7 @@
       <c r="I70" s="6"/>
       <c r="J70" s="6"/>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -11188,7 +11741,7 @@
       <c r="I71" s="4"/>
       <c r="J71" s="4"/>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="5"/>
       <c r="C72" s="3"/>
@@ -11200,7 +11753,7 @@
       <c r="I72" s="6"/>
       <c r="J72" s="6"/>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -11212,7 +11765,7 @@
       <c r="I73" s="4"/>
       <c r="J73" s="4"/>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="5"/>
       <c r="C74" s="3"/>
@@ -11224,7 +11777,7 @@
       <c r="I74" s="6"/>
       <c r="J74" s="6"/>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -11236,7 +11789,7 @@
       <c r="I75" s="4"/>
       <c r="J75" s="4"/>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="5"/>
       <c r="C76" s="3"/>
@@ -11248,7 +11801,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -11260,7 +11813,7 @@
       <c r="I77" s="4"/>
       <c r="J77" s="4"/>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="5"/>
       <c r="C78" s="3"/>
@@ -11272,7 +11825,7 @@
       <c r="I78" s="6"/>
       <c r="J78" s="6"/>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -11284,7 +11837,7 @@
       <c r="I79" s="4"/>
       <c r="J79" s="4"/>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="5"/>
       <c r="C80" s="3"/>
@@ -11296,7 +11849,7 @@
       <c r="I80" s="6"/>
       <c r="J80" s="6"/>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -11308,7 +11861,7 @@
       <c r="I81" s="4"/>
       <c r="J81" s="4"/>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="5"/>
       <c r="C82" s="3"/>
@@ -11320,7 +11873,7 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6"/>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -11332,7 +11885,7 @@
       <c r="I83" s="4"/>
       <c r="J83" s="4"/>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="5"/>
       <c r="C84" s="3"/>
@@ -11344,7 +11897,7 @@
       <c r="I84" s="6"/>
       <c r="J84" s="6"/>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -11356,7 +11909,7 @@
       <c r="I85" s="4"/>
       <c r="J85" s="4"/>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="5"/>
       <c r="C86" s="3"/>
@@ -11368,7 +11921,7 @@
       <c r="I86" s="6"/>
       <c r="J86" s="6"/>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -11380,7 +11933,7 @@
       <c r="I87" s="4"/>
       <c r="J87" s="4"/>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="5"/>
       <c r="C88" s="3"/>
@@ -11392,7 +11945,7 @@
       <c r="I88" s="6"/>
       <c r="J88" s="6"/>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -11404,7 +11957,7 @@
       <c r="I89" s="4"/>
       <c r="J89" s="4"/>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="5"/>
       <c r="C90" s="3"/>
@@ -11416,7 +11969,7 @@
       <c r="I90" s="6"/>
       <c r="J90" s="6"/>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -11428,7 +11981,7 @@
       <c r="I91" s="4"/>
       <c r="J91" s="4"/>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="5"/>
       <c r="C92" s="3"/>
@@ -11440,7 +11993,7 @@
       <c r="I92" s="6"/>
       <c r="J92" s="6"/>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -11452,7 +12005,7 @@
       <c r="I93" s="4"/>
       <c r="J93" s="4"/>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="5"/>
       <c r="C94" s="3"/>
@@ -11464,7 +12017,7 @@
       <c r="I94" s="6"/>
       <c r="J94" s="6"/>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -11476,7 +12029,7 @@
       <c r="I95" s="4"/>
       <c r="J95" s="4"/>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="5"/>
       <c r="C96" s="3"/>
@@ -11488,7 +12041,7 @@
       <c r="I96" s="6"/>
       <c r="J96" s="6"/>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -11500,7 +12053,7 @@
       <c r="I97" s="4"/>
       <c r="J97" s="4"/>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="5"/>
       <c r="C98" s="3"/>
@@ -11512,7 +12065,7 @@
       <c r="I98" s="6"/>
       <c r="J98" s="6"/>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -11524,7 +12077,7 @@
       <c r="I99" s="4"/>
       <c r="J99" s="4"/>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="5"/>
       <c r="C100" s="3"/>
@@ -11536,7 +12089,7 @@
       <c r="I100" s="6"/>
       <c r="J100" s="6"/>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -11548,7 +12101,7 @@
       <c r="I101" s="4"/>
       <c r="J101" s="4"/>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="5"/>
       <c r="C102" s="3"/>
@@ -11560,7 +12113,7 @@
       <c r="I102" s="6"/>
       <c r="J102" s="6"/>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -11572,7 +12125,7 @@
       <c r="I103" s="4"/>
       <c r="J103" s="4"/>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="5"/>
       <c r="C104" s="3"/>
@@ -11584,7 +12137,7 @@
       <c r="I104" s="6"/>
       <c r="J104" s="6"/>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -11596,7 +12149,7 @@
       <c r="I105" s="4"/>
       <c r="J105" s="4"/>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="5"/>
       <c r="C106" s="3"/>
@@ -11608,7 +12161,7 @@
       <c r="I106" s="6"/>
       <c r="J106" s="6"/>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -11620,7 +12173,7 @@
       <c r="I107" s="4"/>
       <c r="J107" s="4"/>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="5"/>
       <c r="C108" s="3"/>
@@ -11632,7 +12185,7 @@
       <c r="I108" s="6"/>
       <c r="J108" s="6"/>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -11644,7 +12197,7 @@
       <c r="I109" s="4"/>
       <c r="J109" s="4"/>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="5"/>
       <c r="C110" s="3"/>
@@ -11656,7 +12209,7 @@
       <c r="I110" s="6"/>
       <c r="J110" s="6"/>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -11668,7 +12221,7 @@
       <c r="I111" s="4"/>
       <c r="J111" s="4"/>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="5"/>
       <c r="C112" s="3"/>
@@ -11680,7 +12233,7 @@
       <c r="I112" s="6"/>
       <c r="J112" s="6"/>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -11692,7 +12245,7 @@
       <c r="I113" s="4"/>
       <c r="J113" s="4"/>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="5"/>
       <c r="C114" s="3"/>
@@ -11704,7 +12257,7 @@
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -11716,7 +12269,7 @@
       <c r="I115" s="4"/>
       <c r="J115" s="4"/>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="5"/>
       <c r="C116" s="3"/>
@@ -11728,7 +12281,7 @@
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -11740,7 +12293,7 @@
       <c r="I117" s="4"/>
       <c r="J117" s="4"/>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="5"/>
       <c r="C118" s="3"/>
@@ -11752,7 +12305,7 @@
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -11764,7 +12317,7 @@
       <c r="I119" s="4"/>
       <c r="J119" s="4"/>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="5"/>
       <c r="C120" s="3"/>
@@ -11776,7 +12329,7 @@
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -11788,7 +12341,7 @@
       <c r="I121" s="4"/>
       <c r="J121" s="4"/>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="5"/>
       <c r="C122" s="3"/>
@@ -11800,7 +12353,7 @@
       <c r="I122" s="6"/>
       <c r="J122" s="6"/>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -11812,7 +12365,7 @@
       <c r="I123" s="4"/>
       <c r="J123" s="4"/>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="5"/>
       <c r="C124" s="3"/>
@@ -11824,7 +12377,7 @@
       <c r="I124" s="6"/>
       <c r="J124" s="6"/>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -11836,7 +12389,7 @@
       <c r="I125" s="4"/>
       <c r="J125" s="4"/>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="5"/>
       <c r="C126" s="3"/>
@@ -11848,7 +12401,7 @@
       <c r="I126" s="6"/>
       <c r="J126" s="6"/>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -11860,7 +12413,7 @@
       <c r="I127" s="4"/>
       <c r="J127" s="4"/>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="5"/>
       <c r="C128" s="3"/>
@@ -11872,7 +12425,7 @@
       <c r="I128" s="6"/>
       <c r="J128" s="6"/>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -11884,7 +12437,7 @@
       <c r="I129" s="4"/>
       <c r="J129" s="4"/>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="5"/>
       <c r="C130" s="3"/>
@@ -11896,7 +12449,7 @@
       <c r="I130" s="6"/>
       <c r="J130" s="6"/>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -11908,7 +12461,7 @@
       <c r="I131" s="4"/>
       <c r="J131" s="4"/>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="5"/>
       <c r="C132" s="3"/>
@@ -11929,18 +12482,18 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{836287F2-96E7-4DEA-9177-5A7142C54641}">
   <dimension ref="A1:J52"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="3" width="11.42578125" customWidth="1"/>
-    <col min="4" max="5" width="26.7109375" customWidth="1"/>
-    <col min="6" max="7" width="13.7109375" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="11.42578125" style="19" customWidth="1"/>
-    <col min="11" max="259" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="3" width="11.44140625" customWidth="1"/>
+    <col min="4" max="5" width="26.6640625" customWidth="1"/>
+    <col min="6" max="7" width="13.6640625" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="10" width="11.44140625" style="19" customWidth="1"/>
+    <col min="11" max="259" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11972,7 +12525,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -12002,7 +12555,7 @@
         <v>45298</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -12032,7 +12585,7 @@
         <v>43738</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -12062,7 +12615,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -12092,7 +12645,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -12122,7 +12675,7 @@
         <v>45596</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -12152,7 +12705,7 @@
         <v>46595</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -12182,7 +12735,7 @@
         <v>46282</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -12212,7 +12765,7 @@
         <v>45230</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -12242,7 +12795,7 @@
         <v>45596</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -12272,7 +12825,7 @@
         <v>45596</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -12302,7 +12855,7 @@
         <v>45382</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -12332,7 +12885,7 @@
         <v>45046</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -12362,7 +12915,7 @@
         <v>44146</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -12392,7 +12945,7 @@
         <v>48183</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -12422,7 +12975,7 @@
         <v>48183</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -12452,7 +13005,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -12482,7 +13035,7 @@
         <v>46995</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -12512,7 +13065,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -12542,7 +13095,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -12572,7 +13125,7 @@
         <v>42978</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -12602,7 +13155,7 @@
         <v>44985</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -12632,7 +13185,7 @@
         <v>45838</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -12662,7 +13215,7 @@
         <v>47362</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -12692,7 +13245,7 @@
         <v>46995</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -12722,7 +13275,7 @@
         <v>47118</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -12752,7 +13305,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -12782,7 +13335,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -12812,7 +13365,7 @@
         <v>46798</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -12842,7 +13395,7 @@
         <v>48549</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -12872,7 +13425,7 @@
         <v>45870</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -12902,7 +13455,7 @@
         <v>45017</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -12932,7 +13485,7 @@
         <v>42521</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -12962,7 +13515,7 @@
         <v>43709</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -12992,7 +13545,7 @@
         <v>44753</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -13022,7 +13575,7 @@
         <v>42063</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -13052,7 +13605,7 @@
         <v>46113</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -13082,7 +13635,7 @@
         <v>46874</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -13112,7 +13665,7 @@
         <v>44501</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -13142,7 +13695,7 @@
         <v>43496</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -13172,7 +13725,7 @@
         <v>43131</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -13202,7 +13755,7 @@
         <v>43769</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -13232,7 +13785,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -13262,7 +13815,7 @@
         <v>44926</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -13292,7 +13845,7 @@
         <v>44732</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -13322,7 +13875,7 @@
         <v>47057</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -13352,7 +13905,7 @@
         <v>47848</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -13382,7 +13935,7 @@
         <v>45351</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -13412,7 +13965,7 @@
         <v>45077</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -13442,7 +13995,7 @@
         <v>45077</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -13472,7 +14025,7 @@
         <v>46873</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -13512,20 +14065,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4691FB44-BBC5-4426-B860-6ED353F70572}">
   <dimension ref="A1:J369"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" customWidth="1"/>
-    <col min="2" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="33.42578125" customWidth="1"/>
-    <col min="5" max="5" width="40.7109375" customWidth="1"/>
-    <col min="6" max="6" width="16.42578125" style="13" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.42578125" customWidth="1"/>
-    <col min="9" max="10" width="11.42578125" style="19" customWidth="1"/>
-    <col min="11" max="250" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" customWidth="1"/>
+    <col min="2" max="3" width="12.33203125" customWidth="1"/>
+    <col min="4" max="4" width="33.44140625" customWidth="1"/>
+    <col min="5" max="5" width="40.6640625" customWidth="1"/>
+    <col min="6" max="6" width="16.44140625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.44140625" customWidth="1"/>
+    <col min="9" max="10" width="11.44140625" style="19" customWidth="1"/>
+    <col min="11" max="250" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13557,7 +14110,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -13589,7 +14142,7 @@
         <v>41737</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -13621,7 +14174,7 @@
         <v>43018</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -13653,7 +14206,7 @@
         <v>44117</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -13685,7 +14238,7 @@
         <v>45027</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -13717,7 +14270,7 @@
         <v>45944</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -13749,7 +14302,7 @@
         <v>40008</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -13781,7 +14334,7 @@
         <v>46752</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -13813,7 +14366,7 @@
         <v>44006</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
@@ -13845,7 +14398,7 @@
         <v>46269</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -13877,7 +14430,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -13909,7 +14462,7 @@
         <v>42151</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -13941,7 +14494,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -13973,7 +14526,7 @@
         <v>45070</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -14005,7 +14558,7 @@
         <v>45770</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -14037,7 +14590,7 @@
         <v>46190</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -14069,7 +14622,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>17</v>
       </c>
@@ -14101,7 +14654,7 @@
         <v>46979</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -14133,7 +14686,7 @@
         <v>41456</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -14165,7 +14718,7 @@
         <v>40360</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -14197,7 +14750,7 @@
         <v>40087</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>21</v>
       </c>
@@ -14229,7 +14782,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -14261,7 +14814,7 @@
         <v>40799</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>23</v>
       </c>
@@ -14293,7 +14846,7 @@
         <v>40799</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -14325,7 +14878,7 @@
         <v>42243</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>25</v>
       </c>
@@ -14357,7 +14910,7 @@
         <v>42243</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -14389,7 +14942,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>27</v>
       </c>
@@ -14421,7 +14974,7 @@
         <v>44196</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -14453,7 +15006,7 @@
         <v>43282</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>29</v>
       </c>
@@ -14485,7 +15038,7 @@
         <v>43282</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -14517,7 +15070,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>31</v>
       </c>
@@ -14549,7 +15102,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -14581,7 +15134,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>33</v>
       </c>
@@ -14613,7 +15166,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -14645,7 +15198,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>35</v>
       </c>
@@ -14677,7 +15230,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -14709,7 +15262,7 @@
         <v>44348</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>37</v>
       </c>
@@ -14741,7 +15294,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -14773,7 +15326,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>39</v>
       </c>
@@ -14805,7 +15358,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -14837,7 +15390,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>41</v>
       </c>
@@ -14869,7 +15422,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -14901,7 +15454,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>43</v>
       </c>
@@ -14933,7 +15486,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -14965,7 +15518,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>45</v>
       </c>
@@ -14997,7 +15550,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -15029,7 +15582,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>47</v>
       </c>
@@ -15061,7 +15614,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -15093,7 +15646,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>49</v>
       </c>
@@ -15125,7 +15678,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -15157,7 +15710,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -15189,7 +15742,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -15221,7 +15774,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -15253,7 +15806,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -15285,7 +15838,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -15317,7 +15870,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -15349,7 +15902,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -15381,7 +15934,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -15413,7 +15966,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -15445,7 +15998,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -15477,7 +16030,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -15509,7 +16062,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -15541,7 +16094,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="2">
         <v>63</v>
       </c>
@@ -15573,7 +16126,7 @@
         <v>46599</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -15605,7 +16158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="2">
         <v>65</v>
       </c>
@@ -15637,7 +16190,7 @@
         <v>44793</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -15669,7 +16222,7 @@
         <v>45329</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="2">
         <v>67</v>
       </c>
@@ -15701,7 +16254,7 @@
         <v>45824</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -15733,7 +16286,7 @@
         <v>47354</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="2">
         <v>69</v>
       </c>
@@ -15765,7 +16318,7 @@
         <v>43861</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -15797,7 +16350,7 @@
         <v>44190</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="2">
         <v>71</v>
       </c>
@@ -15829,7 +16382,7 @@
         <v>44681</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -15861,7 +16414,7 @@
         <v>45468</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="2">
         <v>73</v>
       </c>
@@ -15893,7 +16446,7 @@
         <v>45468</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -15925,7 +16478,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="2">
         <v>75</v>
       </c>
@@ -15957,7 +16510,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -15989,7 +16542,7 @@
         <v>46452</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="2">
         <v>77</v>
       </c>
@@ -16021,7 +16574,7 @@
         <v>46634</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -16053,7 +16606,7 @@
         <v>46908</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="2">
         <v>79</v>
       </c>
@@ -16085,7 +16638,7 @@
         <v>47090</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -16117,7 +16670,7 @@
         <v>47181</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="2">
         <v>81</v>
       </c>
@@ -16149,7 +16702,7 @@
         <v>47271</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -16181,7 +16734,7 @@
         <v>47362</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="2">
         <v>83</v>
       </c>
@@ -16213,7 +16766,7 @@
         <v>47463</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -16245,7 +16798,7 @@
         <v>47544</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="2">
         <v>85</v>
       </c>
@@ -16277,7 +16830,7 @@
         <v>47544</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -16309,7 +16862,7 @@
         <v>47635</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="2">
         <v>87</v>
       </c>
@@ -16341,7 +16894,7 @@
         <v>47635</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="2">
         <v>88</v>
       </c>
@@ -16373,7 +16926,7 @@
         <v>45543</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="2">
         <v>89</v>
       </c>
@@ -16405,7 +16958,7 @@
         <v>45899</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="2">
         <v>90</v>
       </c>
@@ -16437,7 +16990,7 @@
         <v>46046</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="2">
         <v>91</v>
       </c>
@@ -16469,7 +17022,7 @@
         <v>47449</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="2">
         <v>92</v>
       </c>
@@ -16501,7 +17054,7 @@
         <v>47657</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="2">
         <v>93</v>
       </c>
@@ -16533,7 +17086,7 @@
         <v>43352</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="2">
         <v>94</v>
       </c>
@@ -16565,7 +17118,7 @@
         <v>43704</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="2">
         <v>95</v>
       </c>
@@ -16597,7 +17150,7 @@
         <v>45049</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="2">
         <v>96</v>
       </c>
@@ -16629,7 +17182,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="2">
         <v>97</v>
       </c>
@@ -16661,7 +17214,7 @@
         <v>44092</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="2">
         <v>98</v>
       </c>
@@ -16693,7 +17246,7 @@
         <v>43640</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="2">
         <v>99</v>
       </c>
@@ -16725,7 +17278,7 @@
         <v>44317</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="2">
         <v>100</v>
       </c>
@@ -16757,7 +17310,7 @@
         <v>44530</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="2">
         <v>101</v>
       </c>
@@ -16789,7 +17342,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="2">
         <v>102</v>
       </c>
@@ -16821,7 +17374,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="2">
         <v>103</v>
       </c>
@@ -16853,7 +17406,7 @@
         <v>45365</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="2">
         <v>104</v>
       </c>
@@ -16885,7 +17438,7 @@
         <v>44651</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="2">
         <v>105</v>
       </c>
@@ -16917,7 +17470,7 @@
         <v>44355</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="2">
         <v>106</v>
       </c>
@@ -16949,7 +17502,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="2">
         <v>107</v>
       </c>
@@ -16981,7 +17534,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="2">
         <v>108</v>
       </c>
@@ -17013,7 +17566,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="2">
         <v>109</v>
       </c>
@@ -17045,7 +17598,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="2">
         <v>110</v>
       </c>
@@ -17077,7 +17630,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="2">
         <v>111</v>
       </c>
@@ -17109,7 +17662,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="2">
         <v>112</v>
       </c>
@@ -17141,7 +17694,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="2">
         <v>113</v>
       </c>
@@ -17173,7 +17726,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="2">
         <v>114</v>
       </c>
@@ -17205,7 +17758,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="2">
         <v>115</v>
       </c>
@@ -17237,7 +17790,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="2">
         <v>116</v>
       </c>
@@ -17269,7 +17822,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="2">
         <v>117</v>
       </c>
@@ -17301,7 +17854,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="2">
         <v>118</v>
       </c>
@@ -17333,7 +17886,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="2">
         <v>119</v>
       </c>
@@ -17365,7 +17918,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="2">
         <v>120</v>
       </c>
@@ -17397,7 +17950,7 @@
         <v>47483</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="2">
         <v>121</v>
       </c>
@@ -17429,7 +17982,7 @@
         <v>38285</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="2">
         <v>122</v>
       </c>
@@ -17461,7 +18014,7 @@
         <v>43465</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="2">
         <v>123</v>
       </c>
@@ -17493,7 +18046,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="2">
         <v>124</v>
       </c>
@@ -17525,7 +18078,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="2">
         <v>125</v>
       </c>
@@ -17557,7 +18110,7 @@
         <v>42199</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="2">
         <v>126</v>
       </c>
@@ -17589,7 +18142,7 @@
         <v>42745</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="2">
         <v>127</v>
       </c>
@@ -17621,7 +18174,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="2">
         <v>128</v>
       </c>
@@ -17653,7 +18206,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="2">
         <v>129</v>
       </c>
@@ -17685,7 +18238,7 @@
         <v>43018</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="2">
         <v>130</v>
       </c>
@@ -17717,7 +18270,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="2">
         <v>131</v>
       </c>
@@ -17749,7 +18302,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="2">
         <v>132</v>
       </c>
@@ -17781,7 +18334,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="2">
         <v>133</v>
       </c>
@@ -17813,7 +18366,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="2">
         <v>134</v>
       </c>
@@ -17845,7 +18398,7 @@
         <v>44845</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="2">
         <v>135</v>
       </c>
@@ -17877,7 +18430,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="2">
         <v>136</v>
       </c>
@@ -17909,7 +18462,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="2">
         <v>137</v>
       </c>
@@ -17941,7 +18494,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="2">
         <v>138</v>
       </c>
@@ -17973,7 +18526,7 @@
         <v>48590</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="2">
         <v>139</v>
       </c>
@@ -18005,7 +18558,7 @@
         <v>46799</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="2">
         <v>142</v>
       </c>
@@ -18037,7 +18590,7 @@
         <v>45071</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="2">
         <v>143</v>
       </c>
@@ -18069,7 +18622,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="2">
         <v>144</v>
       </c>
@@ -18101,7 +18654,7 @@
         <v>45461</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="2">
         <v>146</v>
       </c>
@@ -18133,7 +18686,7 @@
         <v>47642</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="2">
         <v>147</v>
       </c>
@@ -18165,7 +18718,7 @@
         <v>42836</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="2">
         <v>149</v>
       </c>
@@ -18197,7 +18750,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="2">
         <v>150</v>
       </c>
@@ -18229,7 +18782,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="2">
         <v>152</v>
       </c>
@@ -18261,7 +18814,7 @@
         <v>42791</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="2">
         <v>153</v>
       </c>
@@ -18293,7 +18846,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="2">
         <v>154</v>
       </c>
@@ -18325,7 +18878,7 @@
         <v>40470</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="2">
         <v>155</v>
       </c>
@@ -18357,7 +18910,7 @@
         <v>42825</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="2">
         <v>156</v>
       </c>
@@ -18389,7 +18942,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="2">
         <v>157</v>
       </c>
@@ -18421,7 +18974,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="2">
         <v>158</v>
       </c>
@@ -18453,7 +19006,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="2">
         <v>159</v>
       </c>
@@ -18485,7 +19038,7 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="2">
         <v>160</v>
       </c>
@@ -18517,7 +19070,7 @@
         <v>44228</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="2">
         <v>161</v>
       </c>
@@ -18549,7 +19102,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="2">
         <v>162</v>
       </c>
@@ -18581,7 +19134,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="2">
         <v>163</v>
       </c>
@@ -18613,7 +19166,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="2">
         <v>164</v>
       </c>
@@ -18645,7 +19198,7 @@
         <v>45035</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="2">
         <v>165</v>
       </c>
@@ -18677,7 +19230,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="2">
         <v>166</v>
       </c>
@@ -18709,7 +19262,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="2">
         <v>167</v>
       </c>
@@ -18741,7 +19294,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="2">
         <v>168</v>
       </c>
@@ -18773,7 +19326,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="2">
         <v>169</v>
       </c>
@@ -18805,7 +19358,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="2">
         <v>170</v>
       </c>
@@ -18837,7 +19390,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="2">
         <v>171</v>
       </c>
@@ -18869,7 +19422,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="2">
         <v>172</v>
       </c>
@@ -18901,7 +19454,7 @@
         <v>45931</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="2">
         <v>173</v>
       </c>
@@ -18933,7 +19486,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="2">
         <v>174</v>
       </c>
@@ -18965,7 +19518,7 @@
         <v>45017</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="2">
         <v>175</v>
       </c>
@@ -18997,7 +19550,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="2">
         <v>176</v>
       </c>
@@ -19029,7 +19582,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="2">
         <v>177</v>
       </c>
@@ -19061,7 +19614,7 @@
         <v>44875</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="2">
         <v>178</v>
       </c>
@@ -19093,7 +19646,7 @@
         <v>44875</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="2">
         <v>179</v>
       </c>
@@ -19125,7 +19678,7 @@
         <v>44875</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="2">
         <v>180</v>
       </c>
@@ -19157,7 +19710,7 @@
         <v>44875</v>
       </c>
     </row>
-    <row r="177" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="2">
         <v>181</v>
       </c>
@@ -19189,7 +19742,7 @@
         <v>46519</v>
       </c>
     </row>
-    <row r="178" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="2">
         <v>182</v>
       </c>
@@ -19221,7 +19774,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="179" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="2">
         <v>183</v>
       </c>
@@ -19253,7 +19806,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="180" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="2">
         <v>184</v>
       </c>
@@ -19285,7 +19838,7 @@
         <v>45413</v>
       </c>
     </row>
-    <row r="181" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="2">
         <v>185</v>
       </c>
@@ -19317,7 +19870,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="182" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="2">
         <v>186</v>
       </c>
@@ -19349,7 +19902,7 @@
         <v>44875</v>
       </c>
     </row>
-    <row r="183" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="2">
         <v>187</v>
       </c>
@@ -19381,7 +19934,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="184" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="2">
         <v>188</v>
       </c>
@@ -19413,7 +19966,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="185" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="2">
         <v>189</v>
       </c>
@@ -19445,7 +19998,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="186" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="2">
         <v>190</v>
       </c>
@@ -19477,7 +20030,7 @@
         <v>45239</v>
       </c>
     </row>
-    <row r="187" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="2">
         <v>191</v>
       </c>
@@ -19509,7 +20062,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="188" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="2">
         <v>192</v>
       </c>
@@ -19541,7 +20094,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="189" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="2">
         <v>193</v>
       </c>
@@ -19573,7 +20126,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="190" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="2">
         <v>194</v>
       </c>
@@ -19605,7 +20158,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="191" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="2">
         <v>195</v>
       </c>
@@ -19637,7 +20190,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="192" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="2">
         <v>196</v>
       </c>
@@ -19669,7 +20222,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="193" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="2">
         <v>197</v>
       </c>
@@ -19701,7 +20254,7 @@
         <v>47443</v>
       </c>
     </row>
-    <row r="194" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="2">
         <v>198</v>
       </c>
@@ -19733,7 +20286,7 @@
         <v>45610</v>
       </c>
     </row>
-    <row r="195" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="2">
         <v>199</v>
       </c>
@@ -19765,7 +20318,7 @@
         <v>46042</v>
       </c>
     </row>
-    <row r="196" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="2">
         <v>200</v>
       </c>
@@ -19797,7 +20350,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="197" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="2">
         <v>201</v>
       </c>
@@ -19829,7 +20382,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="198" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="2">
         <v>202</v>
       </c>
@@ -19861,7 +20414,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="199" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="2">
         <v>203</v>
       </c>
@@ -19893,7 +20446,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="200" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="2">
         <v>204</v>
       </c>
@@ -19925,7 +20478,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="201" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="2">
         <v>205</v>
       </c>
@@ -19957,7 +20510,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="202" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="2">
         <v>206</v>
       </c>
@@ -19989,7 +20542,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="203" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="2">
         <v>207</v>
       </c>
@@ -20021,7 +20574,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="204" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="2">
         <v>208</v>
       </c>
@@ -20053,7 +20606,7 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="205" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="2">
         <v>209</v>
       </c>
@@ -20085,7 +20638,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="206" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="2">
         <v>210</v>
       </c>
@@ -20117,7 +20670,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="207" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="2">
         <v>211</v>
       </c>
@@ -20149,7 +20702,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="208" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="2">
         <v>212</v>
       </c>
@@ -20181,7 +20734,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="209" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="2">
         <v>213</v>
       </c>
@@ -20213,7 +20766,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="210" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="2">
         <v>214</v>
       </c>
@@ -20245,7 +20798,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="211" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="2">
         <v>215</v>
       </c>
@@ -20277,7 +20830,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="212" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="2">
         <v>216</v>
       </c>
@@ -20309,7 +20862,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="213" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="2">
         <v>217</v>
       </c>
@@ -20341,7 +20894,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="214" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="2">
         <v>218</v>
       </c>
@@ -20373,7 +20926,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="215" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="2">
         <v>219</v>
       </c>
@@ -20405,7 +20958,7 @@
         <v>46338</v>
       </c>
     </row>
-    <row r="216" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="2">
         <v>220</v>
       </c>
@@ -20437,7 +20990,7 @@
         <v>46702</v>
       </c>
     </row>
-    <row r="217" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="2">
         <v>221</v>
       </c>
@@ -20469,7 +21022,7 @@
         <v>46702</v>
       </c>
     </row>
-    <row r="218" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="2">
         <v>222</v>
       </c>
@@ -20501,7 +21054,7 @@
         <v>46702</v>
       </c>
     </row>
-    <row r="219" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="2">
         <v>223</v>
       </c>
@@ -20533,7 +21086,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="220" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="2">
         <v>224</v>
       </c>
@@ -20565,7 +21118,7 @@
         <v>47010</v>
       </c>
     </row>
-    <row r="221" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="2">
         <v>225</v>
       </c>
@@ -20597,7 +21150,7 @@
         <v>47066</v>
       </c>
     </row>
-    <row r="222" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="2">
         <v>226</v>
       </c>
@@ -20629,7 +21182,7 @@
         <v>47066</v>
       </c>
     </row>
-    <row r="223" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="2">
         <v>227</v>
       </c>
@@ -20661,7 +21214,7 @@
         <v>47066</v>
       </c>
     </row>
-    <row r="224" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="2">
         <v>228</v>
       </c>
@@ -20693,7 +21246,7 @@
         <v>47066</v>
       </c>
     </row>
-    <row r="225" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="2">
         <v>229</v>
       </c>
@@ -20725,7 +21278,7 @@
         <v>47066</v>
       </c>
     </row>
-    <row r="226" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="2">
         <v>230</v>
       </c>
@@ -20757,7 +21310,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="227" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="2">
         <v>231</v>
       </c>
@@ -20789,7 +21342,7 @@
         <v>47430</v>
       </c>
     </row>
-    <row r="228" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="2">
         <v>232</v>
       </c>
@@ -20821,7 +21374,7 @@
         <v>47430</v>
       </c>
     </row>
-    <row r="229" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="2">
         <v>233</v>
       </c>
@@ -20853,7 +21406,7 @@
         <v>47430</v>
       </c>
     </row>
-    <row r="230" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="2">
         <v>234</v>
       </c>
@@ -20885,7 +21438,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="231" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="2">
         <v>235</v>
       </c>
@@ -20917,7 +21470,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="232" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="2">
         <v>236</v>
       </c>
@@ -20949,7 +21502,7 @@
         <v>43048</v>
       </c>
     </row>
-    <row r="233" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="2">
         <v>237</v>
       </c>
@@ -20981,7 +21534,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="234" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="2">
         <v>238</v>
       </c>
@@ -21013,7 +21566,7 @@
         <v>43412</v>
       </c>
     </row>
-    <row r="235" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="2">
         <v>239</v>
       </c>
@@ -21045,7 +21598,7 @@
         <v>43874</v>
       </c>
     </row>
-    <row r="236" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="2">
         <v>240</v>
       </c>
@@ -21077,7 +21630,7 @@
         <v>44238</v>
       </c>
     </row>
-    <row r="237" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="2">
         <v>241</v>
       </c>
@@ -21109,7 +21662,7 @@
         <v>44511</v>
       </c>
     </row>
-    <row r="238" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="2">
         <v>242</v>
       </c>
@@ -21141,7 +21694,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="239" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="2">
         <v>243</v>
       </c>
@@ -21173,7 +21726,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="240" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="2">
         <v>244</v>
       </c>
@@ -21205,7 +21758,7 @@
         <v>45413</v>
       </c>
     </row>
-    <row r="241" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="2">
         <v>245</v>
       </c>
@@ -21237,7 +21790,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="242" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="2">
         <v>246</v>
       </c>
@@ -21269,7 +21822,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="243" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="2">
         <v>247</v>
       </c>
@@ -21301,7 +21854,7 @@
         <v>47239</v>
       </c>
     </row>
-    <row r="244" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="2">
         <v>248</v>
       </c>
@@ -21333,7 +21886,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="245" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="2">
         <v>249</v>
       </c>
@@ -21365,7 +21918,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="246" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="2">
         <v>250</v>
       </c>
@@ -21397,7 +21950,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="247" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="2">
         <v>251</v>
       </c>
@@ -21429,7 +21982,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="248" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="2">
         <v>252</v>
       </c>
@@ -21461,7 +22014,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="249" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="2">
         <v>253</v>
       </c>
@@ -21493,7 +22046,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="250" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="2">
         <v>254</v>
       </c>
@@ -21525,7 +22078,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="251" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="2">
         <v>255</v>
       </c>
@@ -21557,7 +22110,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="252" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="2">
         <v>256</v>
       </c>
@@ -21589,7 +22142,7 @@
         <v>47010</v>
       </c>
     </row>
-    <row r="253" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="2">
         <v>257</v>
       </c>
@@ -21621,7 +22174,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="254" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="2">
         <v>258</v>
       </c>
@@ -21653,7 +22206,7 @@
         <v>41309</v>
       </c>
     </row>
-    <row r="255" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="2">
         <v>259</v>
       </c>
@@ -21685,7 +22238,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="256" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="2">
         <v>260</v>
       </c>
@@ -21717,7 +22270,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="257" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="2">
         <v>261</v>
       </c>
@@ -21749,7 +22302,7 @@
         <v>43922</v>
       </c>
     </row>
-    <row r="258" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="2">
         <v>262</v>
       </c>
@@ -21781,7 +22334,7 @@
         <v>44378</v>
       </c>
     </row>
-    <row r="259" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="2">
         <v>263</v>
       </c>
@@ -21813,7 +22366,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="260" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="2">
         <v>264</v>
       </c>
@@ -21845,7 +22398,7 @@
         <v>45444</v>
       </c>
     </row>
-    <row r="261" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="2">
         <v>265</v>
       </c>
@@ -21877,7 +22430,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="262" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="2">
         <v>266</v>
       </c>
@@ -21909,7 +22462,7 @@
         <v>44105</v>
       </c>
     </row>
-    <row r="263" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="2">
         <v>267</v>
       </c>
@@ -21941,7 +22494,7 @@
         <v>41790</v>
       </c>
     </row>
-    <row r="264" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="2">
         <v>268</v>
       </c>
@@ -21973,7 +22526,7 @@
         <v>43465</v>
       </c>
     </row>
-    <row r="265" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="2">
         <v>269</v>
       </c>
@@ -22005,7 +22558,7 @@
         <v>37437</v>
       </c>
     </row>
-    <row r="266" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="2">
         <v>270</v>
       </c>
@@ -22037,7 +22590,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="267" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="2">
         <v>271</v>
       </c>
@@ -22069,7 +22622,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="268" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="2">
         <v>272</v>
       </c>
@@ -22101,7 +22654,7 @@
         <v>42290</v>
       </c>
     </row>
-    <row r="269" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="2">
         <v>273</v>
       </c>
@@ -22133,7 +22686,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="270" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="2">
         <v>274</v>
       </c>
@@ -22165,7 +22718,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="271" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="2">
         <v>275</v>
       </c>
@@ -22197,7 +22750,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="272" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="2">
         <v>276</v>
       </c>
@@ -22229,7 +22782,7 @@
         <v>41555</v>
       </c>
     </row>
-    <row r="273" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="2">
         <v>277</v>
       </c>
@@ -22261,7 +22814,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="274" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="2">
         <v>278</v>
       </c>
@@ -22293,7 +22846,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="275" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="2">
         <v>279</v>
       </c>
@@ -22325,7 +22878,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="276" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="2">
         <v>280</v>
       </c>
@@ -22357,7 +22910,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="277" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="2">
         <v>281</v>
       </c>
@@ -22389,7 +22942,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="278" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="2">
         <v>282</v>
       </c>
@@ -22421,7 +22974,7 @@
         <v>43382</v>
       </c>
     </row>
-    <row r="279" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="2">
         <v>283</v>
       </c>
@@ -22453,7 +23006,7 @@
         <v>43382</v>
       </c>
     </row>
-    <row r="280" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="2">
         <v>284</v>
       </c>
@@ -22485,7 +23038,7 @@
         <v>43382</v>
       </c>
     </row>
-    <row r="281" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="2">
         <v>285</v>
       </c>
@@ -22517,7 +23070,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="282" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="2">
         <v>286</v>
       </c>
@@ -22549,7 +23102,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="283" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="2">
         <v>287</v>
       </c>
@@ -22581,7 +23134,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="284" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="2">
         <v>288</v>
       </c>
@@ -22613,7 +23166,7 @@
         <v>44754</v>
       </c>
     </row>
-    <row r="285" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="2">
         <v>289</v>
       </c>
@@ -22645,7 +23198,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="286" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="2">
         <v>290</v>
       </c>
@@ -22677,7 +23230,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="287" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="2">
         <v>291</v>
       </c>
@@ -22709,7 +23262,7 @@
         <v>43018</v>
       </c>
     </row>
-    <row r="288" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="2">
         <v>292</v>
       </c>
@@ -22741,7 +23294,7 @@
         <v>43844</v>
       </c>
     </row>
-    <row r="289" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="2">
         <v>293</v>
       </c>
@@ -22773,7 +23326,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="290" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="2">
         <v>294</v>
       </c>
@@ -22805,7 +23358,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="291" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="2">
         <v>295</v>
       </c>
@@ -22837,7 +23390,7 @@
         <v>45482</v>
       </c>
     </row>
-    <row r="292" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="2">
         <v>296</v>
       </c>
@@ -22869,7 +23422,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="293" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="2">
         <v>297</v>
       </c>
@@ -22901,7 +23454,7 @@
         <v>43109</v>
       </c>
     </row>
-    <row r="294" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="2">
         <v>298</v>
       </c>
@@ -22933,7 +23486,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="295" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="2">
         <v>299</v>
       </c>
@@ -22965,7 +23518,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="296" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="2">
         <v>300</v>
       </c>
@@ -22997,7 +23550,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="297" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="2">
         <v>301</v>
       </c>
@@ -23029,7 +23582,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="298" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="2">
         <v>302</v>
       </c>
@@ -23061,7 +23614,7 @@
         <v>43109</v>
       </c>
     </row>
-    <row r="299" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="2">
         <v>303</v>
       </c>
@@ -23093,7 +23646,7 @@
         <v>43655</v>
       </c>
     </row>
-    <row r="300" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="2">
         <v>304</v>
       </c>
@@ -23125,7 +23678,7 @@
         <v>44845</v>
       </c>
     </row>
-    <row r="301" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="2">
         <v>305</v>
       </c>
@@ -23157,7 +23710,7 @@
         <v>44845</v>
       </c>
     </row>
-    <row r="302" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="2">
         <v>306</v>
       </c>
@@ -23189,7 +23742,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="303" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="2">
         <v>307</v>
       </c>
@@ -23221,7 +23774,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="304" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="2">
         <v>308</v>
       </c>
@@ -23253,7 +23806,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="305" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A305" s="2">
         <v>309</v>
       </c>
@@ -23285,7 +23838,7 @@
         <v>46217</v>
       </c>
     </row>
-    <row r="306" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A306" s="2">
         <v>310</v>
       </c>
@@ -23317,7 +23870,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="307" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A307" s="2">
         <v>311</v>
       </c>
@@ -23349,7 +23902,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="308" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A308" s="2">
         <v>312</v>
       </c>
@@ -23381,7 +23934,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="309" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A309" s="2">
         <v>313</v>
       </c>
@@ -23413,7 +23966,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="310" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A310" s="2">
         <v>314</v>
       </c>
@@ -23445,7 +23998,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="311" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A311" s="2">
         <v>315</v>
       </c>
@@ -23477,7 +24030,7 @@
         <v>46672</v>
       </c>
     </row>
-    <row r="312" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A312" s="2">
         <v>316</v>
       </c>
@@ -23509,7 +24062,7 @@
         <v>43837</v>
       </c>
     </row>
-    <row r="313" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A313" s="2">
         <v>317</v>
       </c>
@@ -23541,7 +24094,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="314" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A314" s="2">
         <v>318</v>
       </c>
@@ -23573,7 +24126,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="315" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A315" s="2">
         <v>319</v>
       </c>
@@ -23605,7 +24158,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="316" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A316" s="2">
         <v>320</v>
       </c>
@@ -23637,7 +24190,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="317" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A317" s="2">
         <v>321</v>
       </c>
@@ -23669,7 +24222,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="318" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A318" s="2">
         <v>322</v>
       </c>
@@ -23701,7 +24254,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="319" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A319" s="2">
         <v>323</v>
       </c>
@@ -23733,7 +24286,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="320" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A320" s="2">
         <v>324</v>
       </c>
@@ -23765,7 +24318,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="321" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="321" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A321" s="2">
         <v>325</v>
       </c>
@@ -23797,7 +24350,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="322" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="322" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A322" s="2">
         <v>326</v>
       </c>
@@ -23829,7 +24382,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="323" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="323" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A323" s="2">
         <v>327</v>
       </c>
@@ -23861,7 +24414,7 @@
         <v>47491</v>
       </c>
     </row>
-    <row r="324" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A324" s="2">
         <v>328</v>
       </c>
@@ -23893,7 +24446,7 @@
         <v>48590</v>
       </c>
     </row>
-    <row r="325" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A325" s="2">
         <v>329</v>
       </c>
@@ -23925,7 +24478,7 @@
         <v>48590</v>
       </c>
     </row>
-    <row r="326" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A326" s="2">
         <v>330</v>
       </c>
@@ -23957,7 +24510,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="327" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A327" s="2">
         <v>331</v>
       </c>
@@ -23989,7 +24542,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="328" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A328" s="2">
         <v>332</v>
       </c>
@@ -24021,7 +24574,7 @@
         <v>44971</v>
       </c>
     </row>
-    <row r="329" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A329" s="2">
         <v>333</v>
       </c>
@@ -24053,7 +24606,7 @@
         <v>48590</v>
       </c>
     </row>
-    <row r="330" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A330" s="2">
         <v>334</v>
       </c>
@@ -24085,7 +24638,7 @@
         <v>48590</v>
       </c>
     </row>
-    <row r="331" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A331" s="2">
         <v>335</v>
       </c>
@@ -24117,7 +24670,7 @@
         <v>42472</v>
       </c>
     </row>
-    <row r="332" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A332" s="2">
         <v>336</v>
       </c>
@@ -24149,7 +24702,7 @@
         <v>40190</v>
       </c>
     </row>
-    <row r="333" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A333" s="2">
         <v>337</v>
       </c>
@@ -24181,7 +24734,7 @@
         <v>40918</v>
       </c>
     </row>
-    <row r="334" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A334" s="2">
         <v>338</v>
       </c>
@@ -24213,7 +24766,7 @@
         <v>42472</v>
       </c>
     </row>
-    <row r="335" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A335" s="2">
         <v>339</v>
       </c>
@@ -24245,7 +24798,7 @@
         <v>42472</v>
       </c>
     </row>
-    <row r="336" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A336" s="2">
         <v>340</v>
       </c>
@@ -24277,7 +24830,7 @@
         <v>40736</v>
       </c>
     </row>
-    <row r="337" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A337" s="2">
         <v>341</v>
       </c>
@@ -24309,7 +24862,7 @@
         <v>43200</v>
       </c>
     </row>
-    <row r="338" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="338" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A338" s="2">
         <v>342</v>
       </c>
@@ -24341,7 +24894,7 @@
         <v>44390</v>
       </c>
     </row>
-    <row r="339" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="339" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A339" s="2">
         <v>343</v>
       </c>
@@ -24373,7 +24926,7 @@
         <v>44390</v>
       </c>
     </row>
-    <row r="340" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="340" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A340" s="2">
         <v>344</v>
       </c>
@@ -24405,7 +24958,7 @@
         <v>47413</v>
       </c>
     </row>
-    <row r="341" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="341" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A341" s="2">
         <v>345</v>
       </c>
@@ -24437,7 +24990,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="342" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="342" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A342" s="2">
         <v>346</v>
       </c>
@@ -24469,7 +25022,7 @@
         <v>47077</v>
       </c>
     </row>
-    <row r="343" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="343" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A343" s="2">
         <v>347</v>
       </c>
@@ -24501,7 +25054,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="344" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="344" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A344" s="2">
         <v>348</v>
       </c>
@@ -24533,7 +25086,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="345" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="345" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A345" s="2">
         <v>349</v>
       </c>
@@ -24565,7 +25118,7 @@
         <v>45261</v>
       </c>
     </row>
-    <row r="346" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="346" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A346" s="2">
         <v>350</v>
       </c>
@@ -24597,7 +25150,7 @@
         <v>47269</v>
       </c>
     </row>
-    <row r="347" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="347" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A347" s="2">
         <v>351</v>
       </c>
@@ -24629,7 +25182,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="348" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="348" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A348" s="2">
         <v>352</v>
       </c>
@@ -24661,7 +25214,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="349" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="349" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A349" s="2">
         <v>353</v>
       </c>
@@ -24693,7 +25246,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="350" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="350" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A350" s="2">
         <v>354</v>
       </c>
@@ -24725,7 +25278,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="351" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="351" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A351" s="2">
         <v>355</v>
       </c>
@@ -24757,7 +25310,7 @@
         <v>48365</v>
       </c>
     </row>
-    <row r="352" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="352" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A352" s="2">
         <v>356</v>
       </c>
@@ -24789,7 +25342,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="353" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="353" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A353" s="2">
         <v>357</v>
       </c>
@@ -24821,7 +25374,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="354" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="354" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A354" s="2">
         <v>358</v>
       </c>
@@ -24853,7 +25406,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="355" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="355" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A355" s="2">
         <v>359</v>
       </c>
@@ -24885,7 +25438,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="356" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="356" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A356" s="2">
         <v>360</v>
       </c>
@@ -24917,7 +25470,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="357" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="357" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A357" s="2">
         <v>361</v>
       </c>
@@ -24949,7 +25502,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="358" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="358" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A358" s="2">
         <v>362</v>
       </c>
@@ -24981,7 +25534,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="359" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="359" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A359" s="2">
         <v>363</v>
       </c>
@@ -25013,7 +25566,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="360" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="360" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A360" s="2">
         <v>364</v>
       </c>
@@ -25045,7 +25598,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="361" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="361" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A361" s="2">
         <v>365</v>
       </c>
@@ -25077,7 +25630,7 @@
         <v>44165</v>
       </c>
     </row>
-    <row r="362" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="362" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A362" s="2">
         <v>366</v>
       </c>
@@ -25109,7 +25662,7 @@
         <v>38353</v>
       </c>
     </row>
-    <row r="363" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="363" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A363" s="2">
         <v>367</v>
       </c>
@@ -25141,7 +25694,7 @@
         <v>42206</v>
       </c>
     </row>
-    <row r="364" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="364" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A364" s="2">
         <v>368</v>
       </c>
@@ -25173,7 +25726,7 @@
         <v>42206</v>
       </c>
     </row>
-    <row r="365" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="365" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A365" s="2">
         <v>369</v>
       </c>
@@ -25205,7 +25758,7 @@
         <v>42206</v>
       </c>
     </row>
-    <row r="366" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="366" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A366" s="2">
         <v>370</v>
       </c>
@@ -25237,7 +25790,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="367" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="367" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A367" s="2">
         <v>371</v>
       </c>
@@ -25269,7 +25822,7 @@
         <v>55153</v>
       </c>
     </row>
-    <row r="368" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="368" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A368" s="2">
         <v>372</v>
       </c>
@@ -25301,7 +25854,7 @@
         <v>45473</v>
       </c>
     </row>
-    <row r="369" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="369" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A369" s="2">
         <v>373</v>
       </c>
@@ -25343,13 +25896,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67BCE0F8-676A-4DFA-AC3B-95CC2DE136B8}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="7" max="7" width="23.7109375" customWidth="1"/>
-    <col min="9" max="10" width="10.140625" style="19" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.6640625" customWidth="1"/>
+    <col min="9" max="10" width="10.109375" style="19" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -25381,7 +25934,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -25408,7 +25961,7 @@
         <v>43362</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -25435,7 +25988,7 @@
         <v>43902</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -25462,7 +26015,7 @@
         <v>44515</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -25489,7 +26042,7 @@
         <v>44849</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -25516,7 +26069,7 @@
         <v>45749</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -25543,7 +26096,7 @@
         <v>45749</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -25570,7 +26123,7 @@
         <v>45749</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -25597,7 +26150,7 @@
         <v>47400</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>9</v>
       </c>
